--- a/inventory.xlsx
+++ b/inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\github.com\furqonajiy\itbisa-order-bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15000AE7-C448-428B-9EE8-7E4482ADF8E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A2EB4C2-9A6F-4929-B803-00AA0F189252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1779E557-284E-46C4-9A0B-5BE2FEBFEA49}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>SKU</t>
   </si>
@@ -47,40 +47,7 @@
     <t>Stock</t>
   </si>
   <si>
-    <t>ITBISA-7SEGMENT-CATHODE-RED-2.30-1BIT</t>
-  </si>
-  <si>
-    <t>ITBISA-I2C-IIC-LCD</t>
-  </si>
-  <si>
-    <t>ITBISA-7SEGMENT-CATHODE-RED-0.56-1BIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ITBISA-RELAY-5V-1CHANNEL-BLUE-LOW-TRIGGER</t>
-  </si>
-  <si>
-    <t>ITBISA-IC-74HC245N-DIP20</t>
-  </si>
-  <si>
-    <t>ITBISA-RELAY-5V-5PIN-BLUE</t>
-  </si>
-  <si>
-    <t>ITBISA-RELAY-12V-4PIN-BLUE</t>
-  </si>
-  <si>
-    <t>ITBISA-RELAY-12V-5PIN-BLUE</t>
-  </si>
-  <si>
-    <t>ITBISA-RELAY-5V-4PIN-BLUE</t>
-  </si>
-  <si>
-    <t>ITBISA-IC-CD4094BM-SMD-SOP16</t>
-  </si>
-  <si>
-    <t>ITBISA-IC-NE555P-DIP8</t>
-  </si>
-  <si>
-    <t>ITBISA-WEMOS-D1-MINI-ESP8266</t>
+    <t>ITBISA-IC-L7812CV-TO220</t>
   </si>
 </sst>
 </file>
@@ -452,7 +419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B649193-D86D-4368-BDB9-C95432063B78}">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44.5703125" bestFit="1" customWidth="1"/>
@@ -472,95 +439,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
